--- a/docs/oc-top-organismos/venta-y-arriendo-de-computadores-y-accesorios.xlsx
+++ b/docs/oc-top-organismos/venta-y-arriendo-de-computadores-y-accesorios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M907"/>
+  <dimension ref="A1:M908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1770,7 +1770,11 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>COMPUTACION E INGENIERIA S A</t>
@@ -27417,7 +27421,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2291-350-CM26</t>
+          <t>5520-1492-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27442,32 +27446,32 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -27476,13 +27480,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>11114.06</v>
+        <v>8959.65</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5520-1492-CM26</t>
+          <t>2291-350-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27507,32 +27511,32 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -27541,7 +27545,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>8959.65</v>
+        <v>11114.06</v>
       </c>
     </row>
     <row r="423">
@@ -35089,7 +35093,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -35215,7 +35219,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -39584,7 +39588,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>1460278-203-CM26</t>
+          <t>5434-162-CM26</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -39609,12 +39613,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -39624,28 +39628,32 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K612" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2270.52</v>
+        <v>637</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>5434-162-CM26</t>
+          <t>1460278-203-CM26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -39670,12 +39678,12 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -39685,26 +39693,22 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K613" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr"/>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>637</v>
+        <v>2270.52</v>
       </c>
     </row>
     <row r="614">
@@ -41331,7 +41335,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -42274,7 +42278,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -42469,7 +42473,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -45147,7 +45151,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
@@ -45387,7 +45391,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>564162-578-CM26</t>
+          <t>5610-425-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -45412,12 +45416,12 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -45427,12 +45431,12 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -45446,13 +45450,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3160.64</v>
+        <v>846.05</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>5610-425-CM26</t>
+          <t>3159-108-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -45477,17 +45481,17 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -45511,13 +45515,13 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>846.05</v>
+        <v>5490.07</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>3159-108-CM26</t>
+          <t>564162-578-CM26</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -45542,27 +45546,27 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -45576,7 +45580,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>5490.07</v>
+        <v>3160.64</v>
       </c>
     </row>
     <row r="706">
@@ -45647,7 +45651,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2294-1153-CM26</t>
+          <t>564162-585-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -45667,52 +45671,48 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K707" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>5357.36</v>
+        <v>2158.56</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>5428-17-CM26</t>
+          <t>2294-1153-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -45737,43 +45737,47 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K708" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>2114.93</v>
+        <v>5357.36</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>564162-585-CM26</t>
+          <t>5428-17-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -45798,12 +45802,12 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -45813,12 +45817,12 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K709" t="inlineStr"/>
@@ -45828,7 +45832,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>2158.56</v>
+        <v>2114.93</v>
       </c>
     </row>
     <row r="710">
@@ -46342,7 +46346,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>5872-118-CM26</t>
+          <t>5434-207-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -46397,13 +46401,13 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>1487.49</v>
+        <v>3450.99</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>5434-207-CM26</t>
+          <t>5178-2999-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -46443,12 +46447,12 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K719" t="inlineStr"/>
@@ -46458,13 +46462,13 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>3450.99</v>
+        <v>969.84</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>5178-2999-CM26</t>
+          <t>5178-3000-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -46504,28 +46508,32 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K720" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>969.84</v>
+        <v>892.88</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>5178-3000-CM26</t>
+          <t>5872-118-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -46565,26 +46573,22 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K721" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr"/>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>892.88</v>
+        <v>1487.49</v>
       </c>
     </row>
     <row r="722">
@@ -46996,7 +47000,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
@@ -47439,7 +47443,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
@@ -47829,7 +47833,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
@@ -48020,7 +48024,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
@@ -48333,7 +48337,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
@@ -48524,7 +48528,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
@@ -48752,7 +48756,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>3047-376-CM26</t>
+          <t>5864-40-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -48777,32 +48781,32 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
@@ -48811,13 +48815,13 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>10245.94</v>
+        <v>2713.91</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>3047-376-CM26</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -48842,27 +48846,27 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
@@ -48876,13 +48880,13 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>6369.95</v>
+        <v>10245.94</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>564162-704-CM26</t>
+          <t>5531-165-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -48907,12 +48911,12 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -48922,12 +48926,12 @@
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
@@ -48941,13 +48945,13 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>1956.12</v>
+        <v>1239.48</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>1460278-310-CM26</t>
+          <t>1110404-709-CM26</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -48967,22 +48971,22 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -49006,13 +49010,13 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>9554.93</v>
+        <v>6369.95</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2294-1411-CM26</t>
+          <t>1460278-310-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49037,32 +49041,32 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
@@ -49071,13 +49075,13 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>3956.75</v>
+        <v>9554.93</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2294-1127-CM26</t>
+          <t>2294-1411-CM26</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -49097,7 +49101,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
@@ -49117,28 +49121,32 @@
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K761" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>2384.72</v>
+        <v>3956.75</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>5531-165-CM26</t>
+          <t>2294-1127-CM26</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -49163,47 +49171,43 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K762" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr"/>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>1239.48</v>
+        <v>2384.72</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>564162-704-CM26</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -49223,37 +49227,37 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
@@ -49262,7 +49266,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>2713.91</v>
+        <v>1956.12</v>
       </c>
     </row>
     <row r="764">
@@ -49288,7 +49292,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
@@ -49715,7 +49719,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>3047-394-CM26</t>
+          <t>2294-1469-CM26</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -49735,32 +49739,32 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
@@ -49774,13 +49778,13 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>6449.8</v>
+        <v>33799.97</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>4928-73-CM26</t>
+          <t>1053139-120-CM26</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -49800,52 +49804,48 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K772" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr"/>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>829.3200000000001</v>
+        <v>7556.48</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>1053139-120-CM26</t>
+          <t>4928-73-CM26</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -49865,48 +49865,52 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K773" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>7556.48</v>
+        <v>829.3200000000001</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2294-1469-CM26</t>
+          <t>3047-394-CM26</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -49926,32 +49930,32 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -49965,7 +49969,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>33799.97</v>
+        <v>6449.8</v>
       </c>
     </row>
     <row r="775">
@@ -50166,7 +50170,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>5585-52-CM26</t>
+          <t>4955-121-CM26</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -50186,17 +50190,17 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -50206,12 +50210,12 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
@@ -50225,7 +50229,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>15222.48</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="779">
@@ -50292,7 +50296,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>4955-121-CM26</t>
+          <t>5585-52-CM26</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -50312,17 +50316,17 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -50332,12 +50336,12 @@
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
@@ -50351,7 +50355,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>1064</v>
+        <v>15222.48</v>
       </c>
     </row>
     <row r="781">
@@ -50422,7 +50426,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>4180-130-CM26</t>
+          <t>5434-252-CM26</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -50447,43 +50451,47 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K782" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>6477.17</v>
+        <v>637</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>5434-252-CM26</t>
+          <t>5585-55-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -50503,7 +50511,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
@@ -50523,12 +50531,12 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -50542,13 +50550,13 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>637</v>
+        <v>37184.41</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>5585-55-CM26</t>
+          <t>4180-130-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -50568,52 +50576,48 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K784" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>37184.41</v>
+        <v>6477.17</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>5814-45-CM26</t>
+          <t>1460278-331-CM26</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -50638,12 +50642,12 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -50653,17 +50657,17 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
@@ -50672,13 +50676,13 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>1487.48</v>
+        <v>9554.93</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>1460278-331-CM26</t>
+          <t>5814-45-CM26</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -50703,12 +50707,12 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -50718,17 +50722,17 @@
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L786" t="inlineStr">
@@ -50737,13 +50741,13 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>9554.93</v>
+        <v>1487.48</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>1460278-333-CM26</t>
+          <t>1460278-332-CM26</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -50802,13 +50806,13 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>837.02</v>
+        <v>2380.98</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>5610-507-CM26</t>
+          <t>1460278-333-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -50828,17 +50832,17 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -50848,12 +50852,12 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
@@ -50867,13 +50871,13 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>1014.44</v>
+        <v>837.02</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>564162-754-CM26</t>
+          <t>5610-507-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -50898,12 +50902,12 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -50913,17 +50917,17 @@
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L789" t="inlineStr">
@@ -50932,13 +50936,13 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>4077.32</v>
+        <v>1014.44</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>564162-753-CM26</t>
+          <t>564162-754-CM26</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -50978,28 +50982,32 @@
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K790" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>1902.2</v>
+        <v>4077.32</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>1460278-332-CM26</t>
+          <t>564162-753-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51019,7 +51027,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
@@ -51039,32 +51047,28 @@
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K791" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>2380.98</v>
+        <v>1902.2</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>1053139-125-CM26</t>
+          <t>4928-77-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51084,42 +51088,46 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K792" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>628.03</v>
+        <v>3581.9</v>
       </c>
     </row>
     <row r="793">
@@ -51190,7 +51198,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>4928-77-CM26</t>
+          <t>1053139-125-CM26</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -51215,41 +51223,37 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K794" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr"/>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>3581.9</v>
+        <v>628.03</v>
       </c>
     </row>
     <row r="795">
@@ -51320,7 +51324,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>3134-174-CM26</t>
+          <t>564162-759-CM26</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -51345,41 +51349,37 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K796" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr"/>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>5706.65</v>
+        <v>1487.49</v>
       </c>
     </row>
     <row r="797">
@@ -51446,7 +51446,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>564162-759-CM26</t>
+          <t>3134-174-CM26</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -51471,37 +51471,41 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K798" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>1487.49</v>
+        <v>5706.65</v>
       </c>
     </row>
     <row r="799">
@@ -51568,7 +51572,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>4928-82-CM26</t>
+          <t>1110404-806-CM26</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -51593,27 +51597,27 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
@@ -51627,13 +51631,13 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>4641</v>
+        <v>15721.74</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>5839-37-CM26</t>
+          <t>3474-461-CM26</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -51653,48 +51657,52 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K801" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>11239.07</v>
+        <v>2110.32</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>3474-461-CM26</t>
+          <t>564162-770-CM26</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -51719,12 +51727,12 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -51734,12 +51742,12 @@
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K802" t="inlineStr">
@@ -51753,13 +51761,13 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>2110.32</v>
+        <v>2594.82</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>1110404-806-CM26</t>
+          <t>4928-82-CM26</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -51784,27 +51792,27 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K803" t="inlineStr">
@@ -51818,13 +51826,13 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>15721.74</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>5153-1508-CM26</t>
+          <t>5839-37-CM26</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -51839,7 +51847,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -51849,27 +51857,27 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K804" t="inlineStr"/>
@@ -51879,13 +51887,13 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>4604.76</v>
+        <v>11239.07</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>5684-476-CM26</t>
+          <t>5153-1508-CM26</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -51905,7 +51913,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
@@ -51925,32 +51933,28 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K805" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr"/>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>30617.38</v>
+        <v>4604.76</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>5684-477-CM26</t>
+          <t>5684-476-CM26</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -51990,12 +51994,12 @@
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -52009,13 +52013,13 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>828.24</v>
+        <v>30617.38</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>5684-478-CM26</t>
+          <t>5684-477-CM26</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -52055,28 +52059,32 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K807" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>1135.74</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>5544-8-CM26</t>
+          <t>5684-478-CM26</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -52116,32 +52124,28 @@
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K808" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr"/>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>3718.44</v>
+        <v>1135.74</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>1469-2347-CM26</t>
+          <t>5544-8-CM26</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -52156,53 +52160,57 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K809" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>15261.75</v>
+        <v>3718.44</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>1110404-822-CM26</t>
+          <t>1469-2347-CM26</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -52222,52 +52230,48 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K810" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>4287.75</v>
+        <v>15261.75</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>5574-72-CM26</t>
+          <t>1110404-822-CM26</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -52292,27 +52296,27 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K811" t="inlineStr">
@@ -52326,13 +52330,13 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>49385</v>
+        <v>4287.75</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>1110404-824-CM26</t>
+          <t>5574-72-CM26</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -52357,27 +52361,27 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
@@ -52391,13 +52395,13 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>5555.61</v>
+        <v>49385</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>5543-47-CM26</t>
+          <t>1110404-824-CM26</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -52422,27 +52426,27 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
@@ -52456,13 +52460,13 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>995.64</v>
+        <v>5555.61</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2292-6953-CM26</t>
+          <t>5543-47-CM26</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -52487,43 +52491,47 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K814" t="inlineStr"/>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2719.03</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>5434-279-CM26</t>
+          <t>2292-6953-CM26</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -52538,7 +52546,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -52548,47 +52556,43 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K815" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr"/>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>793.66</v>
+        <v>2719.03</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>5434-281-CM26</t>
+          <t>5434-279-CM26</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -52608,7 +52612,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
@@ -52628,28 +52632,32 @@
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K816" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>296.31</v>
+        <v>793.66</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>5526-55-CM26</t>
+          <t>5434-281-CM26</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -52669,7 +52677,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
@@ -52689,32 +52697,28 @@
       </c>
       <c r="I817" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K817" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr"/>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2022.98</v>
+        <v>296.31</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>5839-38-CM26</t>
+          <t>5526-55-CM26</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -52739,32 +52743,32 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
@@ -52773,13 +52777,13 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>30421.76</v>
+        <v>2022.98</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>1019-284-CM26</t>
+          <t>5839-38-CM26</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -52799,32 +52803,32 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K819" t="inlineStr">
@@ -52838,13 +52842,13 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>1395.04</v>
+        <v>30421.76</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>5434-288-CM26</t>
+          <t>1019-284-CM26</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -52864,17 +52868,17 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -52903,13 +52907,13 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>2380.98</v>
+        <v>1395.04</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>5807-160-CM26</t>
+          <t>5434-288-CM26</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -52924,12 +52928,12 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
@@ -52949,28 +52953,32 @@
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K821" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>1856.39</v>
+        <v>2380.98</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>5807-161-CM26</t>
+          <t>5807-160-CM26</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -53010,12 +53018,12 @@
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K822" t="inlineStr"/>
@@ -53025,13 +53033,13 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>1428</v>
+        <v>1856.39</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>867990-469-CM26</t>
+          <t>5807-161-CM26</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -53046,22 +53054,22 @@
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -53071,32 +53079,28 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K823" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr"/>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>6782.62</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>1110404-835-CM26</t>
+          <t>867990-469-CM26</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -53121,27 +53125,27 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K824" t="inlineStr">
@@ -53155,13 +53159,13 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>2373.01</v>
+        <v>6782.62</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>867990-475-CM26</t>
+          <t>1110404-835-CM26</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -53181,48 +53185,52 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K825" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>3947.65</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>5512-194-CM26</t>
+          <t>867990-475-CM26</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -53247,27 +53255,27 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K826" t="inlineStr"/>
@@ -53277,13 +53285,13 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>3962.7</v>
+        <v>3947.65</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>5769-229-CM26</t>
+          <t>5512-194-CM26</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -53298,37 +53306,37 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K827" t="inlineStr"/>
@@ -53338,13 +53346,13 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>1078.14</v>
+        <v>3962.7</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>976-202-CM26</t>
+          <t>5769-229-CM26</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -53364,17 +53372,17 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -53399,13 +53407,13 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>5226.12</v>
+        <v>1078.14</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>5441-436-CM26</t>
+          <t>976-202-CM26</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -53425,17 +53433,17 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -53445,12 +53453,12 @@
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K829" t="inlineStr"/>
@@ -53460,13 +53468,13 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>6775.86</v>
+        <v>5226.12</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>1110404-847-CM26</t>
+          <t>5441-436-CM26</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -53491,47 +53499,43 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K830" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr"/>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>17150.99</v>
+        <v>6775.86</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>5178-3798-CM26</t>
+          <t>1110404-847-CM26</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -53556,43 +53560,47 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K831" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>5737.13</v>
+        <v>17150.99</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>5178-3805-CM26</t>
+          <t>5178-3798-CM26</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -53632,32 +53640,28 @@
       </c>
       <c r="I832" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K832" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr"/>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>1005.01</v>
+        <v>5737.13</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>5610-529-CM26</t>
+          <t>5178-3805-CM26</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -53672,7 +53676,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -53697,17 +53701,17 @@
       </c>
       <c r="I833" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
@@ -53716,13 +53720,13 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>2334.92</v>
+        <v>1005.01</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>1460278-357-CM26</t>
+          <t>5610-529-CM26</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -53742,17 +53746,17 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
@@ -53762,12 +53766,12 @@
       </c>
       <c r="I834" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K834" t="inlineStr">
@@ -53781,13 +53785,13 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>12102.91</v>
+        <v>2334.92</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>978-130-CM26</t>
+          <t>1460278-357-CM26</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -53802,22 +53806,22 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -53827,28 +53831,32 @@
       </c>
       <c r="I835" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K835" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>12937.68</v>
+        <v>12102.91</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>5951-106-CM26</t>
+          <t>978-130-CM26</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -53863,57 +53871,53 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K836" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr"/>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>18378.36</v>
+        <v>12937.68</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>5434-313-CM26</t>
+          <t>5951-106-CM26</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -53923,47 +53927,47 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
@@ -53972,13 +53976,13 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>326.45</v>
+        <v>18378.36</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>5677-7-CM26</t>
+          <t>5434-313-CM26</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -54018,28 +54022,32 @@
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K838" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>916.3</v>
+        <v>326.45</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>5537-245-CM26</t>
+          <t>5677-7-CM26</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -54059,7 +54067,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -54079,32 +54087,28 @@
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K839" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr"/>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>12211.01</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>3111-38-CM26</t>
+          <t>5537-245-CM26</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -54129,32 +54133,32 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L840" t="inlineStr">
@@ -54163,13 +54167,13 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>3891.54</v>
+        <v>12211.01</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2294-1812-CM26</t>
+          <t>3111-38-CM26</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -54184,42 +54188,42 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L841" t="inlineStr">
@@ -54228,13 +54232,13 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>6069</v>
+        <v>3891.54</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>564162-848-CM26</t>
+          <t>2294-1812-CM26</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -54259,43 +54263,47 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K842" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>3451</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2292-7075-CM26</t>
+          <t>1078177-826-CM26</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -54315,52 +54323,48 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K843" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr"/>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>19312.82</v>
+        <v>1520.82</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>1078177-826-CM26</t>
+          <t>2292-7075-CM26</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -54380,48 +54384,52 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K844" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>1520.82</v>
+        <v>19312.82</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2294-1864-CM26</t>
+          <t>564162-848-CM26</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -54436,7 +54444,7 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -54446,47 +54454,43 @@
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K845" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr"/>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>8039.93</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>1020-278-CM26</t>
+          <t>2294-1864-CM26</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -54501,42 +54505,42 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K846" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L846" t="inlineStr">
@@ -54545,13 +54549,13 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>14522.4</v>
+        <v>8039.93</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>5603-131-CM26</t>
+          <t>1020-278-CM26</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -54571,17 +54575,17 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -54591,28 +54595,32 @@
       </c>
       <c r="I847" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K847" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>2284.8</v>
+        <v>14522.4</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>542343-69-CM26</t>
+          <t>5603-131-CM26</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -54652,32 +54660,28 @@
       </c>
       <c r="I848" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K848" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr"/>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>20091.96</v>
+        <v>2284.8</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>5537-254-CM26</t>
+          <t>542343-69-CM26</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -54692,12 +54696,12 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -54717,22 +54721,26 @@
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K849" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>1402.83</v>
+        <v>20091.96</v>
       </c>
     </row>
     <row r="850">
@@ -54933,7 +54941,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>1469-2718-CM26</t>
+          <t>5537-254-CM26</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -54948,7 +54956,7 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -54958,47 +54966,43 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K853" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr"/>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>22874.78</v>
+        <v>1402.83</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>1018-135-CM26</t>
+          <t>1469-2718-CM26</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -55013,7 +55017,7 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -55023,27 +55027,27 @@
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K854" t="inlineStr">
@@ -55057,13 +55061,13 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>2658.46</v>
+        <v>22874.78</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>3134-194-CM26</t>
+          <t>1018-135-CM26</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -55083,32 +55087,32 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K855" t="inlineStr">
@@ -55122,13 +55126,13 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>251982.5</v>
+        <v>2658.46</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>1110404-911-CM26</t>
+          <t>3134-194-CM26</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -55153,27 +55157,27 @@
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K856" t="inlineStr">
@@ -55187,13 +55191,13 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>18278.4</v>
+        <v>251982.5</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>1110404-910-CM26</t>
+          <t>1110404-911-CM26</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -55213,7 +55217,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
@@ -55233,12 +55237,12 @@
       </c>
       <c r="I857" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K857" t="inlineStr">
@@ -55252,13 +55256,13 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>4133.63</v>
+        <v>18278.4</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>1053139-140-CM26</t>
+          <t>1110404-910-CM26</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -55273,7 +55277,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -55283,12 +55287,12 @@
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -55298,28 +55302,32 @@
       </c>
       <c r="I858" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K858" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>2424.03</v>
+        <v>4133.63</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>5644-11-CM26</t>
+          <t>1053139-140-CM26</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -55334,7 +55342,7 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -55344,47 +55352,43 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K859" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr"/>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>1545.14</v>
+        <v>2424.03</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>5665-2-CM26</t>
+          <t>5644-11-CM26</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -55424,12 +55428,12 @@
       </c>
       <c r="I860" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K860" t="inlineStr">
@@ -55443,13 +55447,13 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>902.25</v>
+        <v>1545.14</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>5603-136-CM26</t>
+          <t>5665-2-CM26</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -55464,12 +55468,12 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -55489,12 +55493,12 @@
       </c>
       <c r="I861" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K861" t="inlineStr">
@@ -55508,13 +55512,13 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>5633.75</v>
+        <v>902.25</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>5441-474-CM26</t>
+          <t>5603-136-CM26</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -55529,7 +55533,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -55554,28 +55558,32 @@
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J862" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K862" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>901.89</v>
+        <v>5633.75</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>5178-4194-CM26</t>
+          <t>5441-474-CM26</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -55615,12 +55623,12 @@
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K863" t="inlineStr"/>
@@ -55630,13 +55638,13 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>758.03</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>867990-568-CM26</t>
+          <t>5178-4194-CM26</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -55651,7 +55659,7 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -55661,12 +55669,12 @@
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -55676,12 +55684,12 @@
       </c>
       <c r="I864" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K864" t="inlineStr"/>
@@ -55691,13 +55699,13 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>6008.31</v>
+        <v>758.03</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>5178-4216-CM26</t>
+          <t>867990-568-CM26</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -55712,7 +55720,7 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -55722,12 +55730,12 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -55737,32 +55745,28 @@
       </c>
       <c r="I865" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K865" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.086.318-1</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr"/>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>3603.32</v>
+        <v>6008.31</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>1053139-145-CM26</t>
+          <t>5178-4216-CM26</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -55777,37 +55781,37 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K866" t="inlineStr">
@@ -55821,13 +55825,13 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>1915.78</v>
+        <v>3603.32</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>867990-582-CM26</t>
+          <t>1053139-145-CM26</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -55847,32 +55851,32 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K867" t="inlineStr">
@@ -55886,13 +55890,13 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>73627.67999999999</v>
+        <v>1915.78</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>867990-587-CM26</t>
+          <t>867990-582-CM26</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -55932,12 +55936,12 @@
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K868" t="inlineStr">
@@ -55951,13 +55955,13 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>73577.11</v>
+        <v>73627.67999999999</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>5585-74-CM26</t>
+          <t>867990-587-CM26</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -55972,22 +55976,22 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -55997,12 +56001,12 @@
       </c>
       <c r="I869" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K869" t="inlineStr">
@@ -56016,13 +56020,13 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>1141.67</v>
+        <v>73577.11</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>5441-486-CM26</t>
+          <t>5585-74-CM26</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -56042,7 +56046,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
@@ -56062,28 +56066,32 @@
       </c>
       <c r="I870" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K870" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>997.78</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>867990-598-CM26</t>
+          <t>5441-486-CM26</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -56108,12 +56116,12 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
@@ -56123,32 +56131,28 @@
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K871" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr"/>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>1141.67</v>
+        <v>997.78</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>1475050-80-CM26</t>
+          <t>867990-598-CM26</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -56163,7 +56167,7 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -56173,12 +56177,12 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -56188,12 +56192,12 @@
       </c>
       <c r="I872" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K872" t="inlineStr">
@@ -56207,13 +56211,13 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>55434.67</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>542343-94-CM26</t>
+          <t>1475050-80-CM26</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -56253,12 +56257,12 @@
       </c>
       <c r="I873" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K873" t="inlineStr">
@@ -56272,13 +56276,13 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>21208.66</v>
+        <v>55434.67</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>5178-4282-CM26</t>
+          <t>542343-94-CM26</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -56298,7 +56302,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
@@ -56318,17 +56322,17 @@
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K874" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L874" t="inlineStr">
@@ -56337,13 +56341,13 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>2344.3</v>
+        <v>21208.66</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>5067-2307-CM26</t>
+          <t>5178-4282-CM26</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -56353,27 +56357,27 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -56383,17 +56387,17 @@
       </c>
       <c r="I875" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K875" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L875" t="inlineStr">
@@ -56402,13 +56406,13 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>12622.9</v>
+        <v>2344.3</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>5542-170-CM26</t>
+          <t>5067-2307-CM26</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -56433,12 +56437,12 @@
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H876" t="inlineStr">
@@ -56448,28 +56452,32 @@
       </c>
       <c r="I876" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K876" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>2165.8</v>
+        <v>12622.9</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>1058758-289-CM26</t>
+          <t>5542-170-CM26</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -56489,52 +56497,48 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K877" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr"/>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>2260.98</v>
+        <v>2165.8</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>5952-165-CM26</t>
+          <t>1058758-289-CM26</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -56574,17 +56578,17 @@
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K878" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L878" t="inlineStr">
@@ -56593,13 +56597,13 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>10810.48</v>
+        <v>2260.98</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>867990-619-CM26</t>
+          <t>5952-165-CM26</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -56619,48 +56623,52 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K879" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>73307.97</v>
+        <v>10810.48</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>553368-155-CM26</t>
+          <t>867990-619-CM26</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -56675,37 +56683,37 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K880" t="inlineStr"/>
@@ -56715,13 +56723,13 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>4517.24</v>
+        <v>73307.97</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>867990-592-CM26</t>
+          <t>553368-155-CM26</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -56741,52 +56749,48 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K881" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr"/>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>15074.86</v>
+        <v>4517.24</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>5655-85-CM26</t>
+          <t>867990-592-CM26</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -56806,17 +56810,17 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -56826,17 +56830,17 @@
       </c>
       <c r="I882" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K882" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L882" t="inlineStr">
@@ -56845,13 +56849,13 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>9008.299999999999</v>
+        <v>15074.86</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>3117-1378-CM26</t>
+          <t>5655-85-CM26</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -56866,7 +56870,7 @@
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -56876,27 +56880,27 @@
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K883" t="inlineStr">
@@ -56910,13 +56914,13 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>693.45</v>
+        <v>9008.299999999999</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>758004-119-CM26</t>
+          <t>3117-1378-CM26</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -56941,27 +56945,27 @@
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K884" t="inlineStr">
@@ -56975,13 +56979,13 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>4403.88</v>
+        <v>693.45</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>1469-3003-CM26</t>
+          <t>758004-119-CM26</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -57006,17 +57010,17 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -57040,13 +57044,13 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>4402.98</v>
+        <v>4403.88</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>5952-168-CM26</t>
+          <t>1469-3003-CM26</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -57061,7 +57065,7 @@
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -57071,27 +57075,27 @@
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J886" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K886" t="inlineStr">
@@ -57105,13 +57109,13 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>7476.18</v>
+        <v>4402.98</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2294-2176-CM26</t>
+          <t>5952-168-CM26</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -57126,7 +57130,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -57136,27 +57140,27 @@
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K887" t="inlineStr">
@@ -57170,13 +57174,13 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>2827.82</v>
+        <v>7476.18</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>1019-346-CM26</t>
+          <t>2294-2176-CM26</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -57201,43 +57205,47 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K888" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>19373.32</v>
+        <v>2827.82</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>1469-3072-CM26</t>
+          <t>1019-346-CM26</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -57252,7 +57260,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -57262,47 +57270,43 @@
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K889" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr"/>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>72503.13</v>
+        <v>19373.32</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>5709-204-CM26</t>
+          <t>1469-3072-CM26</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -57322,48 +57326,52 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K890" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>3510.5</v>
+        <v>72503.13</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>1469-3103-CM26</t>
+          <t>5709-204-CM26</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -57378,37 +57386,37 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K891" t="inlineStr"/>
@@ -57418,13 +57426,13 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>2974.88</v>
+        <v>3510.5</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>1019-350-CM26</t>
+          <t>1469-3103-CM26</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -57449,47 +57457,43 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K892" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr"/>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>71997.98</v>
+        <v>2974.88</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>1053139-170-CM26</t>
+          <t>1019-350-CM26</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -57514,43 +57518,47 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K893" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>57596</v>
+        <v>71997.98</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>3084-155-CM26</t>
+          <t>1053139-170-CM26</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -57565,7 +57573,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -57575,47 +57583,43 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K894" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr"/>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>102525.64</v>
+        <v>57596</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>5178-4486-CM26</t>
+          <t>3084-155-CM26</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -57640,43 +57644,47 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SpA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>77.229.656-8</t>
-        </is>
-      </c>
-      <c r="K895" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>1767.15</v>
+        <v>102525.64</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>1110404-1007-CM26</t>
+          <t>5178-4486-CM26</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -57691,37 +57699,37 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SpA</t>
         </is>
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>77.229.656-8</t>
         </is>
       </c>
       <c r="K896" t="inlineStr"/>
@@ -57731,13 +57739,13 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>4022.15</v>
+        <v>1767.15</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>2294-2250-CM26</t>
+          <t>1110404-1007-CM26</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -57757,52 +57765,48 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K897" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr"/>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>1499.4</v>
+        <v>4022.15</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>1110404-1000-CM26</t>
+          <t>2294-2250-CM26</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -57827,17 +57831,17 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -57861,13 +57865,13 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>1479.17</v>
+        <v>1499.4</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>941739-99-CM26</t>
+          <t>1110404-1000-CM26</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -57882,7 +57886,7 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -57892,12 +57896,12 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -57907,28 +57911,32 @@
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K899" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>4788.54</v>
+        <v>1479.17</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>1110404-1023-CM26</t>
+          <t>941739-99-CM26</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -57953,12 +57961,12 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -57968,32 +57976,28 @@
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J900" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K900" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr"/>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>1206.66</v>
+        <v>4788.54</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>5512-237-CM26</t>
+          <t>1110404-1023-CM26</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -58008,7 +58012,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -58018,12 +58022,12 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H901" t="inlineStr">
@@ -58033,28 +58037,32 @@
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J901" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K901" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>2927.4</v>
+        <v>1206.66</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>5358-316-CM26</t>
+          <t>5512-237-CM26</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -58094,32 +58102,28 @@
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K902" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr"/>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>4259.01</v>
+        <v>2927.4</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>3047-609-CM26</t>
+          <t>5358-316-CM26</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -58144,27 +58148,27 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J903" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K903" t="inlineStr">
@@ -58178,13 +58182,13 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>2912.98</v>
+        <v>4259.01</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>5517-442-CM26</t>
+          <t>3047-609-CM26</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -58199,7 +58203,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -58209,43 +58213,47 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J904" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K904" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>37204.91</v>
+        <v>2912.98</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>5517-437-CM26</t>
+          <t>5517-442-CM26</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -58260,7 +58268,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -58285,32 +58293,28 @@
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J905" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K905" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>8738.93</v>
+        <v>37204.91</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>979-1377-CM26</t>
+          <t>5517-437-CM26</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -58335,12 +58339,12 @@
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
@@ -58350,86 +58354,151 @@
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K906" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>63643.27</v>
+        <v>8738.93</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
+          <t>979-1377-CM26</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr"/>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M907" s="2" t="n">
+        <v>63643.27</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
           <t>5520-6511-CM26</t>
         </is>
       </c>
-      <c r="B907" t="inlineStr">
+      <c r="B908" t="inlineStr">
         <is>
           <t>2239-5-LR25</t>
         </is>
       </c>
-      <c r="C907" t="inlineStr">
+      <c r="C908" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D907" t="inlineStr">
+      <c r="D908" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E907" t="inlineStr">
+      <c r="E908" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr">
+      <c r="F908" t="inlineStr">
         <is>
           <t>60.910.000-1</t>
         </is>
       </c>
-      <c r="G907" t="inlineStr">
+      <c r="G908" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H907" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I907" t="inlineStr">
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
         <is>
           <t>LECHNER S.A</t>
         </is>
       </c>
-      <c r="J907" t="inlineStr">
+      <c r="J908" t="inlineStr">
         <is>
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L907" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M907" s="2" t="n">
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M908" s="2" t="n">
         <v>6532.39</v>
       </c>
     </row>
